--- a/excel/SyntheseComp.xlsx
+++ b/excel/SyntheseComp.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="54">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -546,7 +546,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="67">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -627,6 +627,9 @@
     <xf borderId="20" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf borderId="18" fillId="2" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf borderId="21" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -639,8 +642,14 @@
     <xf borderId="22" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf borderId="17" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="21" fillId="2" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="21" fillId="2" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="17" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="center"/>
@@ -654,8 +663,14 @@
     <xf borderId="22" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
+    <xf borderId="17" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
+    </xf>
     <xf borderId="17" fillId="2" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="21" fillId="2" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -1177,9 +1192,7 @@
       </c>
       <c r="H8" s="29"/>
       <c r="I8" s="30"/>
-      <c r="J8" s="28" t="s">
-        <v>40</v>
-      </c>
+      <c r="J8" s="27"/>
       <c r="K8" s="31"/>
       <c r="L8" s="30"/>
       <c r="M8" s="26"/>
@@ -1194,7 +1207,7 @@
         <v>41</v>
       </c>
       <c r="T8" s="31"/>
-      <c r="U8" s="30"/>
+      <c r="U8" s="32"/>
       <c r="V8" s="26"/>
       <c r="W8" s="26"/>
       <c r="X8" s="31"/>
@@ -1208,38 +1221,36 @@
       <c r="B9" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="32"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="33"/>
-      <c r="F9" s="33"/>
-      <c r="G9" s="34" t="s">
+      <c r="C9" s="33"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="H9" s="35"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="34" t="s">
+      <c r="H9" s="36"/>
+      <c r="I9" s="33"/>
+      <c r="J9" s="37"/>
+      <c r="K9" s="36"/>
+      <c r="L9" s="33"/>
+      <c r="M9" s="34"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="33"/>
+      <c r="P9" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="K9" s="35"/>
-      <c r="L9" s="32"/>
-      <c r="M9" s="33"/>
-      <c r="N9" s="35"/>
-      <c r="O9" s="32"/>
-      <c r="P9" s="34" t="s">
+      <c r="Q9" s="36"/>
+      <c r="R9" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="Q9" s="35"/>
-      <c r="R9" s="36" t="s">
+      <c r="S9" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="S9" s="34" t="s">
-        <v>41</v>
-      </c>
-      <c r="T9" s="35"/>
-      <c r="U9" s="32"/>
-      <c r="V9" s="33"/>
-      <c r="W9" s="33"/>
-      <c r="X9" s="35"/>
+      <c r="T9" s="36"/>
+      <c r="U9" s="39"/>
+      <c r="V9" s="34"/>
+      <c r="W9" s="34"/>
+      <c r="X9" s="36"/>
       <c r="Y9" s="19"/>
       <c r="Z9" s="19"/>
     </row>
@@ -1250,40 +1261,38 @@
       <c r="B10" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="32"/>
-      <c r="D10" s="34" t="s">
+      <c r="C10" s="33"/>
+      <c r="D10" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="34" t="s">
+      <c r="E10" s="34"/>
+      <c r="F10" s="34"/>
+      <c r="G10" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="H10" s="35"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="34" t="s">
+      <c r="H10" s="36"/>
+      <c r="I10" s="33"/>
+      <c r="J10" s="37"/>
+      <c r="K10" s="36"/>
+      <c r="L10" s="33"/>
+      <c r="M10" s="34"/>
+      <c r="N10" s="36"/>
+      <c r="O10" s="33"/>
+      <c r="P10" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="K10" s="35"/>
-      <c r="L10" s="32"/>
-      <c r="M10" s="33"/>
-      <c r="N10" s="35"/>
-      <c r="O10" s="32"/>
-      <c r="P10" s="34" t="s">
+      <c r="Q10" s="36"/>
+      <c r="R10" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="Q10" s="35"/>
-      <c r="R10" s="36" t="s">
+      <c r="S10" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="S10" s="34" t="s">
-        <v>41</v>
-      </c>
-      <c r="T10" s="35"/>
-      <c r="U10" s="32"/>
-      <c r="V10" s="33"/>
-      <c r="W10" s="33"/>
-      <c r="X10" s="35"/>
+      <c r="T10" s="36"/>
+      <c r="U10" s="39"/>
+      <c r="V10" s="34"/>
+      <c r="W10" s="34"/>
+      <c r="X10" s="36"/>
       <c r="Y10" s="19"/>
       <c r="Z10" s="19"/>
     </row>
@@ -1291,124 +1300,120 @@
       <c r="A11" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="37" t="s">
+      <c r="B11" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="38"/>
-      <c r="D11" s="39"/>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="39"/>
-      <c r="H11" s="40"/>
-      <c r="I11" s="38"/>
-      <c r="J11" s="41" t="s">
+      <c r="C11" s="41"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="42"/>
+      <c r="G11" s="42"/>
+      <c r="H11" s="43"/>
+      <c r="I11" s="41"/>
+      <c r="J11" s="44"/>
+      <c r="K11" s="43"/>
+      <c r="L11" s="41"/>
+      <c r="M11" s="42"/>
+      <c r="N11" s="43"/>
+      <c r="O11" s="41"/>
+      <c r="P11" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="K11" s="40"/>
-      <c r="L11" s="38"/>
-      <c r="M11" s="39"/>
-      <c r="N11" s="40"/>
-      <c r="O11" s="38"/>
-      <c r="P11" s="41" t="s">
+      <c r="Q11" s="43"/>
+      <c r="R11" s="41"/>
+      <c r="S11" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="Q11" s="40"/>
-      <c r="R11" s="38"/>
-      <c r="S11" s="41" t="s">
-        <v>41</v>
-      </c>
-      <c r="T11" s="40"/>
-      <c r="U11" s="38"/>
-      <c r="V11" s="39"/>
-      <c r="W11" s="39"/>
-      <c r="X11" s="40"/>
-      <c r="Y11" s="42"/>
-      <c r="Z11" s="42"/>
+      <c r="T11" s="43"/>
+      <c r="U11" s="46"/>
+      <c r="V11" s="42"/>
+      <c r="W11" s="42"/>
+      <c r="X11" s="43"/>
+      <c r="Y11" s="47"/>
+      <c r="Z11" s="47"/>
     </row>
     <row r="12" ht="39.75" customHeight="1">
       <c r="A12" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="B12" s="37" t="s">
+      <c r="B12" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="43" t="s">
+      <c r="C12" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="41" t="s">
+      <c r="D12" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="40"/>
-      <c r="I12" s="38"/>
-      <c r="J12" s="39"/>
-      <c r="K12" s="40"/>
-      <c r="L12" s="38"/>
-      <c r="M12" s="39"/>
-      <c r="N12" s="40"/>
-      <c r="O12" s="38"/>
-      <c r="P12" s="41" t="s">
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="41"/>
+      <c r="J12" s="42"/>
+      <c r="K12" s="43"/>
+      <c r="L12" s="41"/>
+      <c r="M12" s="42"/>
+      <c r="N12" s="43"/>
+      <c r="O12" s="41"/>
+      <c r="P12" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="Q12" s="40"/>
-      <c r="R12" s="43" t="s">
+      <c r="Q12" s="43"/>
+      <c r="R12" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="S12" s="41" t="s">
+      <c r="S12" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="T12" s="40"/>
-      <c r="U12" s="38"/>
-      <c r="V12" s="39"/>
-      <c r="W12" s="39"/>
-      <c r="X12" s="40"/>
-      <c r="Y12" s="42"/>
-      <c r="Z12" s="42"/>
+      <c r="T12" s="43"/>
+      <c r="U12" s="46"/>
+      <c r="V12" s="42"/>
+      <c r="W12" s="42"/>
+      <c r="X12" s="43"/>
+      <c r="Y12" s="47"/>
+      <c r="Z12" s="47"/>
     </row>
     <row r="13" ht="39.75" customHeight="1">
       <c r="A13" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="B13" s="44" t="s">
+      <c r="B13" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="38"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="41" t="s">
+      <c r="C13" s="41"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="F13" s="39"/>
-      <c r="G13" s="39"/>
-      <c r="H13" s="40"/>
-      <c r="I13" s="38"/>
-      <c r="J13" s="41" t="s">
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="41"/>
+      <c r="J13" s="44"/>
+      <c r="K13" s="43"/>
+      <c r="L13" s="41"/>
+      <c r="M13" s="42"/>
+      <c r="N13" s="43"/>
+      <c r="O13" s="41"/>
+      <c r="P13" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="K13" s="40"/>
-      <c r="L13" s="38"/>
-      <c r="M13" s="39"/>
-      <c r="N13" s="40"/>
-      <c r="O13" s="38"/>
-      <c r="P13" s="41" t="s">
+      <c r="Q13" s="43"/>
+      <c r="R13" s="41"/>
+      <c r="S13" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="Q13" s="40"/>
-      <c r="R13" s="38"/>
-      <c r="S13" s="41" t="s">
-        <v>41</v>
-      </c>
-      <c r="T13" s="40"/>
-      <c r="U13" s="38"/>
-      <c r="V13" s="39"/>
-      <c r="W13" s="39"/>
-      <c r="X13" s="40"/>
-      <c r="Y13" s="42"/>
-      <c r="Z13" s="42"/>
+      <c r="T13" s="43"/>
+      <c r="U13" s="46"/>
+      <c r="V13" s="42"/>
+      <c r="W13" s="42"/>
+      <c r="X13" s="43"/>
+      <c r="Y13" s="47"/>
+      <c r="Z13" s="47"/>
     </row>
     <row r="14" ht="31.5" customHeight="1">
-      <c r="A14" s="45" t="s">
+      <c r="A14" s="50" t="s">
         <v>48</v>
       </c>
       <c r="B14" s="21"/>
@@ -1433,7 +1438,7 @@
       <c r="U14" s="21"/>
       <c r="V14" s="21"/>
       <c r="W14" s="21"/>
-      <c r="X14" s="46"/>
+      <c r="X14" s="51"/>
       <c r="Y14" s="19"/>
       <c r="Z14" s="19"/>
     </row>
@@ -1441,48 +1446,48 @@
       <c r="A15" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="B15" s="47" t="s">
+      <c r="B15" s="52" t="s">
         <v>50</v>
       </c>
-      <c r="C15" s="48" t="s">
+      <c r="C15" s="53" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="49"/>
-      <c r="E15" s="50" t="s">
+      <c r="D15" s="54"/>
+      <c r="E15" s="55" t="s">
         <v>41</v>
       </c>
-      <c r="F15" s="49"/>
-      <c r="G15" s="49"/>
-      <c r="H15" s="51"/>
-      <c r="I15" s="52"/>
-      <c r="J15" s="53" t="s">
+      <c r="F15" s="54"/>
+      <c r="G15" s="54"/>
+      <c r="H15" s="56"/>
+      <c r="I15" s="57"/>
+      <c r="J15" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="K15" s="54"/>
-      <c r="L15" s="52"/>
-      <c r="M15" s="55"/>
-      <c r="N15" s="54"/>
-      <c r="O15" s="52"/>
-      <c r="P15" s="53" t="s">
+      <c r="K15" s="59"/>
+      <c r="L15" s="57"/>
+      <c r="M15" s="60"/>
+      <c r="N15" s="59"/>
+      <c r="O15" s="57"/>
+      <c r="P15" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="Q15" s="54"/>
-      <c r="R15" s="56"/>
-      <c r="S15" s="57" t="s">
+      <c r="Q15" s="59"/>
+      <c r="R15" s="61"/>
+      <c r="S15" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="T15" s="54"/>
-      <c r="U15" s="58" t="s">
+      <c r="T15" s="59"/>
+      <c r="U15" s="63" t="s">
         <v>41</v>
       </c>
-      <c r="V15" s="59"/>
-      <c r="W15" s="55"/>
-      <c r="X15" s="54"/>
+      <c r="V15" s="64"/>
+      <c r="W15" s="60"/>
+      <c r="X15" s="59"/>
       <c r="Y15" s="19"/>
       <c r="Z15" s="19"/>
     </row>
     <row r="16" ht="36.75" customHeight="1">
-      <c r="A16" s="45" t="s">
+      <c r="A16" s="50" t="s">
         <v>51</v>
       </c>
       <c r="B16" s="21"/>
@@ -1507,7 +1512,7 @@
       <c r="U16" s="21"/>
       <c r="V16" s="21"/>
       <c r="W16" s="21"/>
-      <c r="X16" s="46"/>
+      <c r="X16" s="51"/>
       <c r="Y16" s="19"/>
       <c r="Z16" s="19"/>
     </row>
@@ -1515,41 +1520,41 @@
       <c r="A17" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="B17" s="47" t="s">
+      <c r="B17" s="52" t="s">
         <v>53</v>
       </c>
-      <c r="C17" s="60"/>
-      <c r="D17" s="49"/>
-      <c r="E17" s="50" t="s">
+      <c r="C17" s="65"/>
+      <c r="D17" s="54"/>
+      <c r="E17" s="55" t="s">
         <v>41</v>
       </c>
-      <c r="F17" s="49"/>
-      <c r="G17" s="49"/>
-      <c r="H17" s="61" t="s">
+      <c r="F17" s="54"/>
+      <c r="G17" s="54"/>
+      <c r="H17" s="66" t="s">
         <v>41</v>
       </c>
-      <c r="I17" s="52"/>
-      <c r="J17" s="53" t="s">
+      <c r="I17" s="57"/>
+      <c r="J17" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="K17" s="54"/>
-      <c r="L17" s="52"/>
-      <c r="M17" s="55"/>
-      <c r="N17" s="54"/>
-      <c r="O17" s="52"/>
-      <c r="P17" s="53" t="s">
+      <c r="K17" s="59"/>
+      <c r="L17" s="57"/>
+      <c r="M17" s="60"/>
+      <c r="N17" s="59"/>
+      <c r="O17" s="57"/>
+      <c r="P17" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="Q17" s="54"/>
-      <c r="R17" s="52"/>
-      <c r="S17" s="53" t="s">
+      <c r="Q17" s="59"/>
+      <c r="R17" s="57"/>
+      <c r="S17" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="T17" s="54"/>
-      <c r="U17" s="52"/>
-      <c r="V17" s="55"/>
-      <c r="W17" s="55"/>
-      <c r="X17" s="54"/>
+      <c r="T17" s="59"/>
+      <c r="U17" s="57"/>
+      <c r="V17" s="60"/>
+      <c r="W17" s="60"/>
+      <c r="X17" s="59"/>
       <c r="Y17" s="19"/>
       <c r="Z17" s="19"/>
     </row>
@@ -11189,12 +11194,12 @@
     <mergeCell ref="C5:H5"/>
     <mergeCell ref="I5:K5"/>
     <mergeCell ref="L5:N5"/>
-    <mergeCell ref="A14:X14"/>
-    <mergeCell ref="A16:X16"/>
     <mergeCell ref="O5:Q5"/>
     <mergeCell ref="R5:T5"/>
     <mergeCell ref="U5:X5"/>
     <mergeCell ref="A7:X7"/>
+    <mergeCell ref="A14:X14"/>
+    <mergeCell ref="A16:X16"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A3:E3"/>
